--- a/data/trans_bre/P16A06-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A06-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 3,65</t>
+          <t>-1,34; 3,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 6,95</t>
+          <t>0,36; 6,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 11,02</t>
+          <t>2,34; 10,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,41; 6,02</t>
+          <t>0,71; 6,01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-75,86; 768,86</t>
+          <t>-71,9; 744,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,32; 636,93</t>
+          <t>-7,44; 679,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,7; 1016,24</t>
+          <t>37,02; 954,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,51; 280,98</t>
+          <t>9,62; 280,96</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 6,96</t>
+          <t>2,21; 6,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 8,22</t>
+          <t>2,32; 8,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,72</t>
+          <t>1,74; 7,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 9,22</t>
+          <t>3,22; 9,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>87,34; 1079,69</t>
+          <t>91,26; 1037,69</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>55,47; 689,13</t>
+          <t>37,35; 668,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,06; 435,06</t>
+          <t>36,81; 432,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>48,6; 275,41</t>
+          <t>43,68; 294,46</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,08</t>
+          <t>-0,27; 2,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,87</t>
+          <t>-1,2; 2,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,75</t>
+          <t>1,67; 6,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 8,16</t>
+          <t>1,17; 8,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-64,2; 406,13</t>
+          <t>-51,63; 384,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>33,84; —</t>
+          <t>64,33; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,01; 178,45</t>
+          <t>14,77; 198,7</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 3,99</t>
+          <t>-0,36; 4,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 8,49</t>
+          <t>2,83; 8,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 10,63</t>
+          <t>3,79; 10,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 5,03</t>
+          <t>-3,7; 5,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,59; 1103,69</t>
+          <t>-42,28; 807,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,65; 935,55</t>
+          <t>75,71; 922,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>102,7; 765,66</t>
+          <t>96,71; 778,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,45; 116,95</t>
+          <t>-40,82; 115,28</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 7,45</t>
+          <t>-0,32; 7,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,9; 21,19</t>
+          <t>9,67; 21,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,43</t>
+          <t>0,79; 10,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 10,82</t>
+          <t>3,94; 10,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 693,28</t>
+          <t>-36,41; 643,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>172,66; 2084,4</t>
+          <t>162,92; 2144,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 532,54</t>
+          <t>-3,21; 619,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>64,1; 459,76</t>
+          <t>67,45; 460,11</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 3,69</t>
+          <t>-0,44; 4,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,6; 6,17</t>
+          <t>0,76; 6,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,9; 11,84</t>
+          <t>3,13; 11,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,19; 11,65</t>
+          <t>2,95; 11,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,3; —</t>
+          <t>-57,68; 1172,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,14; —</t>
+          <t>-33,82; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42,32; 518,45</t>
+          <t>49,28; 500,68</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28,04; 160,72</t>
+          <t>24,82; 152,07</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 3,7</t>
+          <t>-0,12; 3,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,94</t>
+          <t>-0,01; 2,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 6,17</t>
+          <t>0,57; 6,24</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 8,32</t>
+          <t>-1,56; 8,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 270,62</t>
+          <t>-8,38; 275,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 507,77</t>
+          <t>-10,03; 573,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,06; 158,49</t>
+          <t>9,11; 167,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-36,19; 173,28</t>
+          <t>-20,57; 167,6</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 4,46</t>
+          <t>-0,0; 4,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,9</t>
+          <t>2,19; 7,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,23</t>
+          <t>2,61; 6,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,67; 9,07</t>
+          <t>3,61; 9,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 152,09</t>
+          <t>-1,36; 147,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>54,03; 330,42</t>
+          <t>51,49; 324,94</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>125,2; 994,68</t>
+          <t>111,28; 1075,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>83,4; 549,31</t>
+          <t>84,03; 523,09</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,07</t>
+          <t>1,37; 3,02</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,19; 5,29</t>
+          <t>3,17; 5,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,81; 5,95</t>
+          <t>3,8; 6,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3,35; 6,54</t>
+          <t>2,96; 6,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>58,98; 192,36</t>
+          <t>57,82; 186,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>124,9; 305,31</t>
+          <t>124,49; 312,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>123,51; 268,22</t>
+          <t>120,81; 265,86</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>62,99; 158,24</t>
+          <t>60,65; 167,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A06-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P16A06-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,35</t>
+          <t>2,51</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>68,29%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 3,86</t>
+          <t>-1,19; 3,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 6,94</t>
+          <t>0,31; 7,39</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,34; 10,96</t>
+          <t>2,96; 10,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,01</t>
+          <t>-0,19; 4,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-71,9; 744,72</t>
+          <t>-73,09; 726,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 679,54</t>
+          <t>-16,77; 603,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,02; 954,33</t>
+          <t>57,06; 1024,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,62; 280,96</t>
+          <t>-6,11; 198,33</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,36</t>
+          <t>5,82</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>129,53%</t>
+          <t>113,21%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 6,76</t>
+          <t>2,13; 6,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,32; 8,44</t>
+          <t>2,34; 8,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 7,17</t>
+          <t>1,6; 7,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 9,61</t>
+          <t>2,66; 8,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>91,26; 1037,69</t>
+          <t>80,7; 934,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,35; 668,45</t>
+          <t>42,71; 668,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,81; 432,19</t>
+          <t>36,6; 427,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>43,68; 294,46</t>
+          <t>37,41; 238,74</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,9</t>
+          <t>4,48</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>71,39%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 2,11</t>
+          <t>-0,27; 2,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,87</t>
+          <t>-1,53; 2,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 6,65</t>
+          <t>1,67; 6,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,17; 8,62</t>
+          <t>0,61; 7,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-51,63; 384,62</t>
+          <t>-68,75; 442,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,33; —</t>
+          <t>30,22; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,77; 198,7</t>
+          <t>4,52; 175,02</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,18</t>
+          <t>3,47</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>62,27%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 4,14</t>
+          <t>-0,36; 4,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 8,72</t>
+          <t>2,6; 8,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,79; 10,61</t>
+          <t>4,03; 10,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 5,05</t>
+          <t>-0,27; 7,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,28; 807,34</t>
+          <t>-33,82; 981,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,71; 922,37</t>
+          <t>68,83; 882,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,71; 778,44</t>
+          <t>99,65; 889,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,82; 115,28</t>
+          <t>-5,41; 215,71</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,06</t>
+          <t>7,11</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>190,68%</t>
+          <t>213,33%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 7,21</t>
+          <t>-0,1; 7,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,67; 21,23</t>
+          <t>8,78; 20,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,79; 10,34</t>
+          <t>0,5; 9,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,94; 10,59</t>
+          <t>4,05; 10,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-36,41; 643,27</t>
+          <t>-15,64; 951,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>162,92; 2144,04</t>
+          <t>158,65; 1843,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 619,52</t>
+          <t>-7,36; 539,64</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>67,45; 460,11</t>
+          <t>70,14; 530,16</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,3</t>
+          <t>7,49</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>83,26%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 4,03</t>
+          <t>-0,54; 3,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,0</t>
+          <t>0,71; 6,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,13; 11,83</t>
+          <t>2,79; 11,65</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,95; 11,43</t>
+          <t>3,28; 11,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-57,68; 1172,94</t>
+          <t>-68,12; 993,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,82; —</t>
+          <t>-22,65; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,28; 500,68</t>
+          <t>39,92; 506,89</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>24,82; 152,07</t>
+          <t>27,19; 161,74</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,02</t>
+          <t>6,97</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>125,82%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 3,69</t>
+          <t>-0,12; 3,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 2,99</t>
+          <t>-0,1; 3,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,57; 6,24</t>
+          <t>0,46; 6,21</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 8,24</t>
+          <t>3,79; 9,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 275,16</t>
+          <t>-7,89; 288,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 573,58</t>
+          <t>-15,86; 474,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,11; 167,03</t>
+          <t>4,96; 174,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-20,57; 167,6</t>
+          <t>50,36; 229,34</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,9</t>
+          <t>4,26</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>198,51%</t>
+          <t>109,41%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 4,38</t>
+          <t>0,09; 4,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,19; 7,03</t>
+          <t>2,45; 7,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,5</t>
+          <t>2,61; 6,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,61; 9,24</t>
+          <t>2,19; 6,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 147,66</t>
+          <t>1,57; 161,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,49; 324,94</t>
+          <t>54,27; 330,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>111,28; 1075,86</t>
+          <t>132,27; 1110,34</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>84,03; 523,09</t>
+          <t>43,62; 206,79</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4,99</t>
+          <t>5,23</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>102,84%</t>
+          <t>101,63%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,02</t>
+          <t>1,39; 3,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,17; 5,18</t>
+          <t>3,22; 5,19</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,8; 6,04</t>
+          <t>3,83; 5,94</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,96; 6,42</t>
+          <t>4,15; 6,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>57,82; 186,96</t>
+          <t>59,81; 182,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>124,49; 312,54</t>
+          <t>127,29; 316,8</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>120,81; 265,86</t>
+          <t>122,72; 266,97</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>60,65; 167,14</t>
+          <t>73,06; 139,2</t>
         </is>
       </c>
     </row>
